--- a/XLibur.Tests/Resource/Examples/Comments/AddingComments.xlsx
+++ b/XLibur.Tests/Resource/Examples/Comments/AddingComments.xlsx
@@ -1376,7 +1376,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D5"/>
+  <x:dimension ref="A1:D9"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="4" width="9.140625" style="0" customWidth="1"/>
